--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.52315319521339</v>
+        <v>4.310012394222175</v>
       </c>
       <c r="D2" t="n">
-        <v>26.98549546659307</v>
+        <v>4.385143013321374</v>
       </c>
       <c r="E2" t="n">
-        <v>10.45783659701295</v>
+        <v>1.699398447014605</v>
       </c>
       <c r="F2" t="n">
-        <v>7.622492697237845</v>
+        <v>1.23865506330115</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.14344668738969</v>
+        <v>5.548310086700825</v>
       </c>
       <c r="D3" t="n">
-        <v>5.165920926258288</v>
+        <v>0.8394621505169718</v>
       </c>
       <c r="E3" t="n">
-        <v>10.45783659701295</v>
+        <v>1.699398447014605</v>
       </c>
       <c r="F3" t="n">
-        <v>7.622492697237845</v>
+        <v>1.23865506330115</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.40411341010338</v>
+        <v>3.965668429141799</v>
       </c>
       <c r="D4" t="n">
-        <v>24.88982523816324</v>
+        <v>4.044596601201527</v>
       </c>
       <c r="E4" t="n">
-        <v>10.45783659701295</v>
+        <v>1.699398447014605</v>
       </c>
       <c r="F4" t="n">
-        <v>7.622492697237845</v>
+        <v>1.23865506330115</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.10338909369573</v>
+        <v>2.454300727725556</v>
       </c>
       <c r="D5" t="n">
-        <v>15.60232624400915</v>
+        <v>2.535378014651488</v>
       </c>
       <c r="E5" t="n">
-        <v>10.45783659701295</v>
+        <v>1.699398447014605</v>
       </c>
       <c r="F5" t="n">
-        <v>7.622492697237845</v>
+        <v>1.23865506330115</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.44454697298053</v>
+        <v>1.859738883109337</v>
       </c>
       <c r="D6" t="n">
-        <v>10.97852181248782</v>
+        <v>1.784009794529271</v>
       </c>
       <c r="E6" t="n">
-        <v>10.45783659701295</v>
+        <v>1.699398447014605</v>
       </c>
       <c r="F6" t="n">
-        <v>7.622492697237845</v>
+        <v>1.23865506330115</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>2.604522624384658</v>
+        <v>0.423234926462507</v>
       </c>
       <c r="D7" t="n">
-        <v>19.96987923586364</v>
+        <v>3.245105375827842</v>
       </c>
       <c r="E7" t="n">
-        <v>10.45783659701295</v>
+        <v>1.699398447014605</v>
       </c>
       <c r="F7" t="n">
-        <v>7.622492697237845</v>
+        <v>1.23865506330115</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
